--- a/ig/improve-doc/CodeSystem-terminologie-standardterms.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-standardterms.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-standardterms</t>
+    <t>OID:0.4.0.127.0.16.1.1.2.1</t>
   </si>
   <si>
     <t>Version</t>
